--- a/google-ads-copy-aurora.xlsx
+++ b/google-ads-copy-aurora.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Precios Desde $150 por Uña</t>
+          <t>Precios Desde $225 por Uña</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Clínica podológica con precios accesibles desde $150. Certificada y con experiencia.</t>
+          <t>Clínica podológica con precios accesibles desde $225. Certificada y con experiencia.</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Tratamiento de Uñeros $200</t>
+          <t>Tratamiento de Uñeros $300</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Solo $200 por Uña - Agenda</t>
+          <t>Solo $300 por Uña - Agenda</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Tratamiento profesional de uñas encarnadas desde $200. Extracción segura y sin dolor.</t>
+          <t>Tratamiento profesional de uñas encarnadas desde $300. Extracción segura y sin dolor.</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Precios Justos - Desde $150</t>
+          <t>Precios Justos - Desde $225</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Trato personalizado y profesional. Precios accesibles desde $150. Sin cita previa.</t>
+          <t>Trato personalizado y profesional. Precios accesibles desde $225. Sin cita previa.</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Tratamiento desde $200 por uña</t>
+          <t>Tratamiento desde $300 por uña</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Onicomicosis desde $165 por uña</t>
+          <t>Onicomicosis desde $248 por uña</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Eliminación de callosidades $500</t>
+          <t>Eliminación de callosidades $750</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Cuidado integral de pies $440</t>
+          <t>Cuidado integral de pies $450</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>$165</t>
+          <t>$248</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>$200</t>
+          <t>$300</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>$150</t>
+          <t>$225</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>$750</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>$440</t>
+          <t>$450</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
